--- a/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C69CC4EE-7FDE-40A0-98C8-9DE829880B03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC4EDD2E-C3EE-4ABD-BB8C-F35AEDF746DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB0F7146-DBBB-4C92-A327-3515388109E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20BCB1B6-8FB1-4157-8BAD-ED2481D54C06}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D56BA67-D722-43B9-898F-9949FE52B546}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA513B89-2235-4C92-851B-3B2509CEAA01}"/>
 </file>